--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.67510277812358</v>
+        <v>8.234704201445082</v>
       </c>
       <c r="D2" t="n">
-        <v>50.8270584210474</v>
+        <v>8.259396993420202</v>
       </c>
       <c r="E2" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F2" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.25990227788789</v>
+        <v>3.292234120156782</v>
       </c>
       <c r="D3" t="n">
-        <v>20.38545803571573</v>
+        <v>3.312636930803807</v>
       </c>
       <c r="E3" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F3" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.61630126252203</v>
+        <v>4.00014895515983</v>
       </c>
       <c r="D4" t="n">
-        <v>24.77763762932926</v>
+        <v>4.026366114766005</v>
       </c>
       <c r="E4" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F4" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.50858921916188</v>
+        <v>4.632645748113806</v>
       </c>
       <c r="D5" t="n">
-        <v>28.63052375165798</v>
+        <v>4.652460109644422</v>
       </c>
       <c r="E5" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F5" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.07660811303574</v>
+        <v>3.749948818368308</v>
       </c>
       <c r="D6" t="n">
-        <v>23.18253166999004</v>
+        <v>3.767161396373382</v>
       </c>
       <c r="E6" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F6" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.31060096276429</v>
+        <v>7.850472656449197</v>
       </c>
       <c r="D7" t="n">
-        <v>48.59024198027232</v>
+        <v>7.895914321794253</v>
       </c>
       <c r="E7" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F7" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.84194269360013</v>
+        <v>7.774315687710022</v>
       </c>
       <c r="D8" t="n">
-        <v>47.3785246447699</v>
+        <v>7.699010254775108</v>
       </c>
       <c r="E8" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F8" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.255974361844713</v>
+        <v>1.341595833799766</v>
       </c>
       <c r="D9" t="n">
-        <v>8.138018222379527</v>
+        <v>1.322427961136673</v>
       </c>
       <c r="E9" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F9" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74095344661676</v>
+        <v>5.320404935075223</v>
       </c>
       <c r="D10" t="n">
-        <v>32.79026409167233</v>
+        <v>5.328417914896753</v>
       </c>
       <c r="E10" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F10" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.90814512328933</v>
+        <v>2.747573582534517</v>
       </c>
       <c r="D11" t="n">
-        <v>16.75602327277076</v>
+        <v>2.722853781825248</v>
       </c>
       <c r="E11" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F11" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.5879876860974</v>
+        <v>5.458047998990827</v>
       </c>
       <c r="D12" t="n">
-        <v>34.33597677994917</v>
+        <v>5.57959622674174</v>
       </c>
       <c r="E12" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F12" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.68494199958836</v>
+        <v>5.311303074933109</v>
       </c>
       <c r="D13" t="n">
-        <v>33.65791829804787</v>
+        <v>5.469411723432779</v>
       </c>
       <c r="E13" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F13" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.3905727588419</v>
+        <v>5.750968073311808</v>
       </c>
       <c r="D14" t="n">
-        <v>34.56121518157645</v>
+        <v>5.616197467006174</v>
       </c>
       <c r="E14" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F14" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.22520529243616</v>
+        <v>6.374095860020877</v>
       </c>
       <c r="D15" t="n">
-        <v>24.34893844635772</v>
+        <v>3.95670249753313</v>
       </c>
       <c r="E15" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F15" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>29.36473636505448</v>
+        <v>4.771769659321352</v>
       </c>
       <c r="D16" t="n">
-        <v>28.32399753322809</v>
+        <v>4.602649599149564</v>
       </c>
       <c r="E16" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F16" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>39.91345187163805</v>
+        <v>6.485935929141182</v>
       </c>
       <c r="D17" t="n">
-        <v>20.61152653642849</v>
+        <v>3.349373062169629</v>
       </c>
       <c r="E17" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F17" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>38.62081788309067</v>
+        <v>6.275882906002233</v>
       </c>
       <c r="D18" t="n">
-        <v>35.71619282161339</v>
+        <v>5.803881333512176</v>
       </c>
       <c r="E18" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F18" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>48.42042651227067</v>
+        <v>7.868319308243984</v>
       </c>
       <c r="D19" t="n">
-        <v>15.18444904747845</v>
+        <v>2.467472970215248</v>
       </c>
       <c r="E19" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F19" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>47.09610614232648</v>
+        <v>7.653117248128054</v>
       </c>
       <c r="D20" t="n">
-        <v>13.45221985935228</v>
+        <v>2.185985727144746</v>
       </c>
       <c r="E20" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F20" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>34.38915525537255</v>
+        <v>5.58823772899804</v>
       </c>
       <c r="D21" t="n">
-        <v>33.19942172579481</v>
+        <v>5.394906030441658</v>
       </c>
       <c r="E21" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F21" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>14.73719727458784</v>
+        <v>2.394794557120523</v>
       </c>
       <c r="D22" t="n">
-        <v>13.73914906133736</v>
+        <v>2.232611722467321</v>
       </c>
       <c r="E22" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F22" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>30.26367541106445</v>
+        <v>4.917847254297974</v>
       </c>
       <c r="D23" t="n">
-        <v>22.57486433726915</v>
+        <v>3.668415454806237</v>
       </c>
       <c r="E23" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F23" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>46.85488309674253</v>
+        <v>7.613918503220661</v>
       </c>
       <c r="D24" t="n">
-        <v>16.77958057901061</v>
+        <v>2.726681844089224</v>
       </c>
       <c r="E24" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F24" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>42.03640461152302</v>
+        <v>6.83091574937249</v>
       </c>
       <c r="D25" t="n">
-        <v>40.84315295204255</v>
+        <v>6.637012354706915</v>
       </c>
       <c r="E25" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F25" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>48.66899072096208</v>
+        <v>7.908710992156338</v>
       </c>
       <c r="D26" t="n">
-        <v>39.66781929929653</v>
+        <v>6.446020636135685</v>
       </c>
       <c r="E26" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F26" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>49.15898225695765</v>
+        <v>7.988334616755618</v>
       </c>
       <c r="D27" t="n">
-        <v>47.96715956998749</v>
+        <v>7.794663430122966</v>
       </c>
       <c r="E27" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F27" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>18.36894092224647</v>
+        <v>2.984952899865051</v>
       </c>
       <c r="D28" t="n">
-        <v>18.81177422761973</v>
+        <v>3.056913311988206</v>
       </c>
       <c r="E28" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F28" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>31.79667634205707</v>
+        <v>5.166959905584274</v>
       </c>
       <c r="D29" t="n">
-        <v>30.47722661187152</v>
+        <v>4.952549324429122</v>
       </c>
       <c r="E29" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F29" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>58.34300397331314</v>
+        <v>9.480738145663386</v>
       </c>
       <c r="D30" t="n">
-        <v>57.24475970498199</v>
+        <v>9.302273452059573</v>
       </c>
       <c r="E30" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F30" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>29.59853907168876</v>
+        <v>4.809762599149424</v>
       </c>
       <c r="D31" t="n">
-        <v>30.23353096335548</v>
+        <v>4.912948781545266</v>
       </c>
       <c r="E31" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F31" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>57.53490694523373</v>
+        <v>9.349422378600481</v>
       </c>
       <c r="D32" t="n">
-        <v>56.48142154795459</v>
+        <v>9.178231001542621</v>
       </c>
       <c r="E32" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F32" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>60.59607867707982</v>
+        <v>9.84686278502547</v>
       </c>
       <c r="D33" t="n">
-        <v>59.6883226807122</v>
+        <v>9.699352435615733</v>
       </c>
       <c r="E33" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F33" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>47.28672772121329</v>
+        <v>7.68409325469716</v>
       </c>
       <c r="D34" t="n">
-        <v>47.64374740899516</v>
+        <v>7.742108953961714</v>
       </c>
       <c r="E34" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F34" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>69.88748642703545</v>
+        <v>11.35671654439326</v>
       </c>
       <c r="D35" t="n">
-        <v>69.04379823136908</v>
+        <v>11.21961721259748</v>
       </c>
       <c r="E35" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F35" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>48.79341060308809</v>
+        <v>7.928929223001815</v>
       </c>
       <c r="D36" t="n">
-        <v>48.84544635991811</v>
+        <v>7.937385033486692</v>
       </c>
       <c r="E36" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F36" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>53.71502065064947</v>
+        <v>8.728690855730539</v>
       </c>
       <c r="D37" t="n">
-        <v>46.30738138040558</v>
+        <v>7.524949474315907</v>
       </c>
       <c r="E37" t="n">
-        <v>14.00114360394275</v>
+        <v>2.275185835640697</v>
       </c>
       <c r="F37" t="n">
-        <v>14.9111073595138</v>
+        <v>2.423054945920993</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
